--- a/data/trans_dic/IP1004-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1004-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen diabetes</t>
+          <t>Menores que padecen diabetes (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,66</t>
+          <t>0,0; 4,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,39</t>
+          <t>0,0; 4,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 2,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,62</t>
+          <t>0,0; 6,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,0; 3,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,65</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 0,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,09</t>
+          <t>0,46; 4,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,32</t>
+          <t>0,26; 2,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,8</t>
+          <t>0,0; 4,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1338,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,68</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1347,37 +1348,37 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,05</t>
+          <t>0,18; 1,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,72</t>
+          <t>0,15; 0,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,49</t>
+          <t>0,03; 0,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,38</t>
+          <t>0,0; 0,36</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen diabetes (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1568</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4019</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4193</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4758</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5682</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4789</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3389</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3224</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3100</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2703</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3766</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3368</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3750</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3871</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>591; 5408</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>593; 5672</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2993</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3232</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>3255</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1522</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>4671</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2312</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 5033</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3965</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4776</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1264; 7290</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 5327</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1924; 9136</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>416; 6875</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0; 5005</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1004-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1004-Clase-trans_dic.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,54</t>
+          <t>0,0; 4,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,67</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,67</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,5</t>
+          <t>0,0; 6,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,41</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,25</t>
+          <t>0,47; 4,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,45</t>
+          <t>0,26; 2,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 0,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,06</t>
+          <t>0,19; 1,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,69</t>
+          <t>0,15; 0,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,5</t>
+          <t>0,05; 0,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,36</t>
+          <t>0,0; 0,34</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4019</t>
+          <t>0; 3988</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4193</t>
+          <t>0; 3647</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4758</t>
+          <t>0; 5529</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5682</t>
+          <t>0; 5549</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4789</t>
+          <t>0; 4878</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3389</t>
+          <t>0; 3084</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3224</t>
+          <t>0; 3515</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2138,17 +2138,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3100</t>
+          <t>0; 3865</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2703</t>
+          <t>0; 3990</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3766</t>
+          <t>0; 3719</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2158,17 +2158,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3368</t>
+          <t>0; 3359</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3750</t>
+          <t>0; 3533</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3871</t>
+          <t>0; 3113</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>591; 5408</t>
+          <t>593; 5867</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>593; 5672</t>
+          <t>593; 5307</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2993</t>
+          <t>0; 2990</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3232</t>
+          <t>0; 2983</t>
         </is>
       </c>
     </row>
@@ -2617,29 +2617,29 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0; 5561</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4480</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4780</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1285; 7300</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
           <t>0; 5033</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>0; 3965</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0; 4776</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1264; 7290</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>0; 5327</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -2647,17 +2647,17 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1924; 9136</t>
+          <t>1956; 9248</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>416; 6875</t>
+          <t>743; 6163</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 5005</t>
+          <t>0; 4653</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1004-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1004-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -630,22 +630,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,51</t>
+          <t>0,0; 4,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,06</t>
+          <t>0,0; 4,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -735,22 +735,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>1,62%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,34%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,32 +1008,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,46; 4,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,29</t>
+          <t>0,26; 2,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1185,22 +1185,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>0,96%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,22%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,12%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,17; 1,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,66</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,07</t>
+          <t>0,0; 0,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,7</t>
+          <t>0,15; 0,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,44</t>
+          <t>0,05; 0,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,34</t>
+          <t>0,0; 0,38</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1591,22 +1591,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>790</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>777</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3988</t>
+          <t>0; 3939</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3647</t>
+          <t>0; 4119</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5529</t>
+          <t>0; 5440</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1749,22 +1749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1415</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5549</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4914</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4878</t>
+          <t>0; 4353</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>618</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3124</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3084</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3515</t>
+          <t>0; 3130</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>667</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>744</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>771</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3871</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3739</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3865</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3990</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3719</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4254</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3359</t>
+          <t>0; 3351</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3533</t>
+          <t>0; 5092</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3113</t>
+          <t>0; 3122</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>590; 5200</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>593; 5867</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>593; 5307</t>
+          <t>593; 5364</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2411,22 +2411,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>589</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2990</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2935</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 2983</t>
+          <t>0; 2969</t>
         </is>
       </c>
     </row>
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>3255</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1522</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>1415</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>790</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>1360</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>3255</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1522</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5561</t>
+          <t>1138; 7176</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4480</t>
+          <t>0; 5259</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4780</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1285; 7300</t>
+          <t>0; 4326</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 5033</t>
+          <t>0; 3975</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4987</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1956; 9248</t>
+          <t>2019; 9523</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>743; 6163</t>
+          <t>742; 6854</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4653</t>
+          <t>0; 5305</t>
         </is>
       </c>
     </row>
